--- a/TITAN_A5/BD.xlsx
+++ b/TITAN_A5/BD.xlsx
@@ -19,12 +19,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="4">
   <si>
-    <t>Включил HLLD</t>
+    <t>Laks</t>
   </si>
   <si>
-    <t>HLL</t>
+    <t>HLL + time = 10</t>
+  </si>
+  <si>
+    <t>TVD</t>
+  </si>
+  <si>
+    <t>доустановил предыдущий расчёт</t>
   </si>
 </sst>
 </file>
@@ -60,8 +66,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -334,7 +343,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -342,50 +351,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" customWidth="1"/>
-    <col min="2" max="2" width="21.7265625" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7265625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="33.1796875" style="1" customWidth="1"/>
+    <col min="5" max="12" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1">
+    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1.2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>1.3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="10" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>

--- a/TITAN_A5/BD.xlsx
+++ b/TITAN_A5/BD.xlsx
@@ -19,18 +19,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
   <si>
     <t>Laks</t>
-  </si>
-  <si>
-    <t>HLL + time = 10</t>
   </si>
   <si>
     <t>TVD</t>
   </si>
   <si>
     <t>доустановил предыдущий расчёт</t>
+  </si>
+  <si>
+    <t>HLL + time = 0.4</t>
+  </si>
+  <si>
+    <t>HLLC + time = 0.4</t>
   </si>
 </sst>
 </file>
@@ -343,7 +346,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -369,7 +372,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -380,10 +383,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -391,13 +394,23 @@
         <v>1.3</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
     </row>
-    <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>

--- a/TITAN_A5/BD.xlsx
+++ b/TITAN_A5/BD.xlsx
@@ -19,34 +19,758 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
-  <si>
-    <t>Laks</t>
-  </si>
-  <si>
-    <t>TVD</t>
-  </si>
-  <si>
-    <t>доустановил предыдущий расчёт</t>
-  </si>
-  <si>
-    <t>HLL + time = 0.4</t>
-  </si>
-  <si>
-    <t>HLLC + time = 0.4</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+  <si>
+    <t>HLL (при x &gt; 0)</t>
+  </si>
+  <si>
+    <t>Разделил силу на 100</t>
+  </si>
+  <si>
+    <t>0.2  0.001  1.0   100.0</t>
+  </si>
+  <si>
+    <t>HLLD (17) + HLL</t>
+  </si>
+  <si>
+    <t>Без коллебаний - базовое решение</t>
+  </si>
+  <si>
+    <t>HLL (r &lt; 260)</t>
+  </si>
+  <si>
+    <t>HLL + HLLD</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> par_pi_8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> dev_time_all</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>3.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
+    <t>HLL</t>
+  </si>
+  <si>
+    <t>там где-то плотность отрицательной становится - надо исправлять</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> par_pi_8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> dev_time_all</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>6.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
+    <t>пробую включить HLLD с ограничением по плотности</t>
+  </si>
+  <si>
+    <t>HLLD-</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> par_pi_8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> dev_time_all</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>/9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>))</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF3B3B3B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3B3B3B"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF3B3B3B"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFD4922F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -69,9 +793,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -355,75 +1094,122 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="33.1796875" style="1" customWidth="1"/>
-    <col min="5" max="12" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="18.81640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="21.7265625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="22.08984375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="79.6328125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="109.36328125" style="1" customWidth="1"/>
+    <col min="6" max="12" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="D2" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
+    <row r="3" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
+    <row r="4" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="5"/>
     </row>
-    <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>1.4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>1</v>
+    <row r="5" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="10" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="17" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -433,5 +1219,6 @@
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/TITAN_A5/BD.xlsx
+++ b/TITAN_A5/BD.xlsx
@@ -1,30 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="11020"/>
+    <workbookView windowWidth="30720" windowHeight="13440"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+  <si>
+    <t>parameters_A5-2_0001.bin</t>
+  </si>
   <si>
     <t>HLL (при x &gt; 0)</t>
-  </si>
-  <si>
-    <t>Разделил силу на 100</t>
   </si>
   <si>
     <t>0.2  0.001  1.0   100.0</t>
@@ -33,237 +41,231 @@
     <t>HLLD (17) + HLL</t>
   </si>
   <si>
-    <t>Без коллебаний - базовое решение</t>
+    <t>Разделил силу на 100</t>
   </si>
   <si>
     <t>HLL (r &lt; 260)</t>
   </si>
   <si>
-    <t>HLL + HLLD</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">dd </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>1.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>0.7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>sin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>2.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> par_pi_8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> dev_time_all</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>3.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>))</t>
-    </r>
+    <t>Без коллебаний - базовое решение</t>
   </si>
   <si>
     <t>HLL</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">dd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> par_pi_8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> dev_time_all</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>3.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
+    <t>HLL + HLLD</t>
+  </si>
+  <si>
     <t>там где-то плотность отрицательной становится - надо исправлять</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
       <t xml:space="preserve">dd </t>
     </r>
     <r>
@@ -271,7 +273,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>=</t>
@@ -281,7 +282,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> (</t>
@@ -291,7 +291,6 @@
         <sz val="10"/>
         <color rgb="FFD4922F"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>1.0</t>
@@ -301,7 +300,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -311,7 +309,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>+</t>
@@ -321,7 +318,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -331,7 +327,6 @@
         <sz val="10"/>
         <color rgb="FFD4922F"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>0.7</t>
@@ -341,7 +336,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -351,7 +345,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>*</t>
@@ -361,7 +354,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -371,7 +363,6 @@
         <sz val="10"/>
         <color rgb="FF0000FF"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>sin</t>
@@ -381,7 +372,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>(</t>
@@ -391,7 +381,6 @@
         <sz val="10"/>
         <color rgb="FFD4922F"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>2.0</t>
@@ -401,7 +390,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -411,7 +399,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>*</t>
@@ -421,7 +408,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> par_pi_8 </t>
@@ -431,7 +417,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>*</t>
@@ -441,7 +426,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> dev_time_all</t>
@@ -451,7 +435,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>/</t>
@@ -461,7 +444,6 @@
         <sz val="10"/>
         <color rgb="FFD4922F"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>6.0</t>
@@ -471,7 +453,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>))</t>
@@ -485,6 +466,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
       <t xml:space="preserve">dd </t>
     </r>
     <r>
@@ -492,7 +479,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>=</t>
@@ -502,7 +488,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> (</t>
@@ -512,7 +497,6 @@
         <sz val="10"/>
         <color rgb="FFD4922F"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>1.0</t>
@@ -522,7 +506,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -532,7 +515,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>+</t>
@@ -542,7 +524,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -552,7 +533,6 @@
         <sz val="10"/>
         <color rgb="FFD4922F"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>0.7</t>
@@ -562,7 +542,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -572,7 +551,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>*</t>
@@ -582,7 +560,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -592,7 +569,6 @@
         <sz val="10"/>
         <color rgb="FF0000FF"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>sin</t>
@@ -602,7 +578,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>(</t>
@@ -612,7 +587,6 @@
         <sz val="10"/>
         <color rgb="FFD4922F"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>2.0</t>
@@ -622,7 +596,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -632,7 +605,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>*</t>
@@ -642,7 +614,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> par_pi_8 </t>
@@ -652,7 +623,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>*</t>
@@ -662,7 +632,6 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> dev_time_all</t>
@@ -672,7 +641,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>/9</t>
@@ -682,7 +650,6 @@
         <sz val="10"/>
         <color rgb="FFD4922F"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>.0</t>
@@ -692,23 +659,37 @@
         <sz val="10"/>
         <color rgb="FF3B3B3B"/>
         <rFont val="Consolas"/>
-        <family val="3"/>
         <charset val="204"/>
       </rPr>
       <t>))</t>
     </r>
+  </si>
+  <si>
+    <t>parameters_A5-3_0001.bin</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>Сетка с 4.000.000 ячеек. Достаточно подробная. 10.000 шагов делает за 7 минут. Время за шаг около 1.3 10^-4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -716,7 +697,14 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
@@ -725,63 +713,386 @@
       <sz val="12"/>
       <color rgb="FF3B3B3B"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color rgb="FF3B3B3B"/>
+      <name val="Consolas"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3B3B3B"/>
       <name val="Consolas"/>
-      <family val="3"/>
       <charset val="204"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF3B3B3B"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-      <charset val="204"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Consolas"/>
-      <family val="3"/>
       <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFD4922F"/>
       <name val="Consolas"/>
-      <family val="3"/>
       <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Consolas"/>
-      <family val="3"/>
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -789,16 +1100,264 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -814,17 +1373,61 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
+    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
+    <cellStyle name="Процент" xfId="3" builtinId="5"/>
+    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
+    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
+    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
+    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
+    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
+    <cellStyle name="Итого" xfId="21" builtinId="25"/>
+    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
+    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
+    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1082,143 +1685,165 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="21.7265625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="22.08984375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="79.6328125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="109.36328125" style="1" customWidth="1"/>
-    <col min="6" max="12" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="18.8148148148148" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7222222222222" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.0925925925926" style="2" customWidth="1"/>
+    <col min="4" max="4" width="79.6296296296296" style="2" customWidth="1"/>
+    <col min="5" max="5" width="109.361111111111" style="3" customWidth="1"/>
+    <col min="6" max="12" width="8.72222222222222" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" ht="29" customHeight="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
+    </row>
+    <row r="2" ht="27.5" customHeight="1" spans="1:5">
+      <c r="A2" s="4">
+        <v>2.2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="3" ht="27.5" customHeight="1" spans="1:5">
+      <c r="A3" s="4">
+        <v>2.3</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
+    <row r="4" ht="27.5" customHeight="1" spans="1:5">
+      <c r="A4" s="4">
         <v>2.4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3" t="s">
-        <v>4</v>
+      <c r="C4" s="5"/>
+      <c r="D4" s="6" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
+    <row r="5" ht="27.5" customHeight="1" spans="1:5">
+      <c r="A5" s="4">
         <v>2.5</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="6" t="s">
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" ht="27.5" customHeight="1" spans="1:5">
+      <c r="A6" s="4">
+        <v>2.6</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" ht="27.5" customHeight="1" spans="1:5">
+      <c r="A7" s="4">
+        <v>2.7</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
-        <v>2.6</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="8" ht="27.5" customHeight="1" spans="1:5">
+      <c r="A8" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" ht="27.5" customHeight="1" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" ht="27.5" customHeight="1" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>9</v>
+      <c r="E10" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
-        <v>2.7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
-        <v>2.8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="10" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="11" ht="27.5" customHeight="1"/>
+    <row r="12" ht="27.5" customHeight="1"/>
+    <row r="13" ht="27.5" customHeight="1"/>
+    <row r="14" ht="27.5" customHeight="1"/>
+    <row r="15" ht="27.5" customHeight="1"/>
+    <row r="16" ht="27.5" customHeight="1"/>
+    <row r="17" ht="27.5" customHeight="1"/>
+    <row r="18" ht="27.5" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="24" customHeight="1"/>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A9:C9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/TITAN_A5/BD.xlsx
+++ b/TITAN_A5/BD.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13440"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="11020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
   <si>
     <t>parameters_A5-2_0001.bin</t>
   </si>
@@ -672,19 +672,25 @@
   </si>
   <si>
     <t>Сетка с 4.000.000 ячеек. Достаточно подробная. 10.000 шагов делает за 7 минут. Время за шаг около 1.3 10^-4</t>
+  </si>
+  <si>
+    <t>2.9</t>
+  </si>
+  <si>
+    <t>2.7 пересчитал новой схемой</t>
+  </si>
+  <si>
+    <t>2.10</t>
+  </si>
+  <si>
+    <t>2.4 пересчитал новой схемой</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="29">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -729,157 +735,6 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Consolas"/>
@@ -898,201 +753,15 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1100,253 +769,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1372,58 +799,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
-    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
-    <cellStyle name="Процент" xfId="3" builtinId="5"/>
-    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
-    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
-    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
-    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
-    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
-    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
-    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
-    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
-    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
-    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
-    <cellStyle name="Итого" xfId="21" builtinId="25"/>
-    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
-    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
-    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
-    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
-    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
-    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
-    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
-    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
-    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1685,31 +1071,33 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="18.8148148148148" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7222222222222" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22.0925925925926" style="2" customWidth="1"/>
-    <col min="4" max="4" width="79.6296296296296" style="2" customWidth="1"/>
-    <col min="5" max="5" width="109.361111111111" style="3" customWidth="1"/>
-    <col min="6" max="12" width="8.72222222222222" style="3"/>
+    <col min="1" max="1" width="18.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.08984375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="79.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="109.36328125" style="3" customWidth="1"/>
+    <col min="6" max="12" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="29" customHeight="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="29" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
     </row>
-    <row r="2" ht="27.5" customHeight="1" spans="1:5">
+    <row r="2" spans="1:5" ht="27.5" customHeight="1">
       <c r="A2" s="4">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -1719,9 +1107,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="27.5" customHeight="1" spans="1:5">
+    <row r="3" spans="1:5" ht="27.5" customHeight="1">
       <c r="A3" s="4">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>3</v>
@@ -1733,7 +1121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="27.5" customHeight="1" spans="1:5">
+    <row r="4" spans="1:5" ht="27.5" customHeight="1">
       <c r="A4" s="4">
         <v>2.4</v>
       </c>
@@ -1745,7 +1133,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="27.5" customHeight="1" spans="1:5">
+    <row r="5" spans="1:5" ht="27.5" customHeight="1">
       <c r="A5" s="4">
         <v>2.5</v>
       </c>
@@ -1758,7 +1146,7 @@
       </c>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" ht="27.5" customHeight="1" spans="1:5">
+    <row r="6" spans="1:5" ht="27.5" customHeight="1">
       <c r="A6" s="4">
         <v>2.6</v>
       </c>
@@ -1773,7 +1161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="27.5" customHeight="1" spans="1:5">
+    <row r="7" spans="1:5" ht="27.5" customHeight="1">
       <c r="A7" s="4">
         <v>2.7</v>
       </c>
@@ -1788,7 +1176,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" ht="27.5" customHeight="1" spans="1:5">
+    <row r="8" spans="1:5" ht="27.5" customHeight="1">
       <c r="A8" s="1">
         <v>2.8</v>
       </c>
@@ -1803,47 +1191,76 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="27.5" customHeight="1" spans="1:5">
+    <row r="9" spans="1:5" ht="27.5" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="10" ht="27.5" customHeight="1" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="1:5" ht="27.5" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>13</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="3" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="27.5" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+    </row>
+    <row r="12" spans="1:5" ht="27.5" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" ht="27.5" customHeight="1"/>
-    <row r="12" ht="27.5" customHeight="1"/>
-    <row r="13" ht="27.5" customHeight="1"/>
-    <row r="14" ht="27.5" customHeight="1"/>
-    <row r="15" ht="27.5" customHeight="1"/>
-    <row r="16" ht="27.5" customHeight="1"/>
+    <row r="13" spans="1:5" ht="27.5" customHeight="1"/>
+    <row r="14" spans="1:5" ht="27.5" customHeight="1"/>
+    <row r="15" spans="1:5" ht="27.5" customHeight="1"/>
+    <row r="16" spans="1:5" ht="27.5" customHeight="1"/>
     <row r="17" ht="27.5" customHeight="1"/>
     <row r="18" ht="27.5" customHeight="1"/>
-    <row r="19" ht="24" customHeight="1"/>
-    <row r="20" ht="24" customHeight="1"/>
+    <row r="19" ht="27.5" customHeight="1"/>
+    <row r="20" ht="27.5" customHeight="1"/>
     <row r="21" ht="24" customHeight="1"/>
     <row r="22" ht="24" customHeight="1"/>
     <row r="23" ht="24" customHeight="1"/>
     <row r="24" ht="24" customHeight="1"/>
     <row r="25" ht="24" customHeight="1"/>
+    <row r="26" ht="24" customHeight="1"/>
+    <row r="27" ht="24" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A11:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/TITAN_A5/BD.xlsx
+++ b/TITAN_A5/BD.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
   <si>
     <t>parameters_A5-2_0001.bin</t>
   </si>
@@ -684,6 +684,406 @@
   </si>
   <si>
     <t>2.4 пересчитал новой схемой</t>
+  </si>
+  <si>
+    <t>2.11</t>
+  </si>
+  <si>
+    <t>2.4 пересчитал новой схемой (меньше ограничений)</t>
+  </si>
+  <si>
+    <t>2.12</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> par_pi_8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> dev_time_all</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
+    <t>2.13</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> par_pi_8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> dev_time_all</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>))</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1077,7 +1477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="18.81640625" style="1" customWidth="1"/>
@@ -1219,46 +1619,84 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="27.5" customHeight="1">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:5" ht="41.5" customHeight="1">
+      <c r="A11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="41.5" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="41.5" customHeight="1">
+      <c r="A13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="27.5" customHeight="1">
+      <c r="A14" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
     </row>
-    <row r="12" spans="1:5" ht="27.5" customHeight="1">
-      <c r="A12" s="1" t="s">
+    <row r="15" spans="1:5" ht="27.5" customHeight="1">
+      <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D15" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="27.5" customHeight="1"/>
-    <row r="14" spans="1:5" ht="27.5" customHeight="1"/>
-    <row r="15" spans="1:5" ht="27.5" customHeight="1"/>
     <row r="16" spans="1:5" ht="27.5" customHeight="1"/>
     <row r="17" ht="27.5" customHeight="1"/>
     <row r="18" ht="27.5" customHeight="1"/>
     <row r="19" ht="27.5" customHeight="1"/>
     <row r="20" ht="27.5" customHeight="1"/>
-    <row r="21" ht="24" customHeight="1"/>
-    <row r="22" ht="24" customHeight="1"/>
-    <row r="23" ht="24" customHeight="1"/>
+    <row r="21" ht="27.5" customHeight="1"/>
+    <row r="22" ht="27.5" customHeight="1"/>
+    <row r="23" ht="27.5" customHeight="1"/>
     <row r="24" ht="24" customHeight="1"/>
     <row r="25" ht="24" customHeight="1"/>
     <row r="26" ht="24" customHeight="1"/>
     <row r="27" ht="24" customHeight="1"/>
+    <row r="28" ht="24" customHeight="1"/>
+    <row r="29" ht="24" customHeight="1"/>
+    <row r="30" ht="24" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/TITAN_A5/BD.xlsx
+++ b/TITAN_A5/BD.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="11020"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>parameters_A5-2_0001.bin</t>
   </si>
@@ -665,6 +665,627 @@
     </r>
   </si>
   <si>
+    <t>2.9</t>
+  </si>
+  <si>
+    <t>2.7 пересчитал новой схемой</t>
+  </si>
+  <si>
+    <t>2.10</t>
+  </si>
+  <si>
+    <t>2.4 пересчитал новой схемой</t>
+  </si>
+  <si>
+    <t>2.11</t>
+  </si>
+  <si>
+    <t>2.4 пересчитал новой схемой (меньше ограничений)</t>
+  </si>
+  <si>
+    <t>2.12</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">dd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> par_pi_8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> dev_time_all</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
+    <t>2.13</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">dd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> par_pi_8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> dev_time_all</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
+    <t>2.14</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> par_pi_8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> dev_time_all</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
     <t>parameters_A5-3_0001.bin</t>
   </si>
   <si>
@@ -672,425 +1293,19 @@
   </si>
   <si>
     <t>Сетка с 4.000.000 ячеек. Достаточно подробная. 10.000 шагов делает за 7 минут. Время за шаг около 1.3 10^-4</t>
-  </si>
-  <si>
-    <t>2.9</t>
-  </si>
-  <si>
-    <t>2.7 пересчитал новой схемой</t>
-  </si>
-  <si>
-    <t>2.10</t>
-  </si>
-  <si>
-    <t>2.4 пересчитал новой схемой</t>
-  </si>
-  <si>
-    <t>2.11</t>
-  </si>
-  <si>
-    <t>2.4 пересчитал новой схемой (меньше ограничений)</t>
-  </si>
-  <si>
-    <t>2.12</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">dd </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>1.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>0.1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>sin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>2.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> par_pi_8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> dev_time_all</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>0.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>))</t>
-    </r>
-  </si>
-  <si>
-    <t>2.13</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">dd </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>1.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>0.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>sin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>2.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> par_pi_8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> dev_time_all</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>0.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>))</t>
-    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1135,6 +1350,150 @@
       <charset val="204"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Consolas"/>
@@ -1153,15 +1512,201 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1169,11 +1714,253 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1199,17 +1986,58 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
+    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
+    <cellStyle name="Процент" xfId="3" builtinId="5"/>
+    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
+    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
+    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
+    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
+    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
+    <cellStyle name="Итого" xfId="21" builtinId="25"/>
+    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
+    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
+    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1471,33 +2299,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22.08984375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="79.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="109.36328125" style="3" customWidth="1"/>
-    <col min="6" max="12" width="8.7265625" style="3"/>
+    <col min="1" max="1" width="18.8148148148148" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7222222222222" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.0925925925926" style="2" customWidth="1"/>
+    <col min="4" max="4" width="79.6296296296296" style="2" customWidth="1"/>
+    <col min="5" max="5" width="109.361111111111" style="3" customWidth="1"/>
+    <col min="6" max="12" width="8.72222222222222" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="29" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" ht="29" customHeight="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
     </row>
-    <row r="2" spans="1:5" ht="27.5" customHeight="1">
+    <row r="2" ht="27.5" customHeight="1" spans="1:5">
       <c r="A2" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -1507,9 +2333,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="27.5" customHeight="1">
+    <row r="3" ht="27.5" customHeight="1" spans="1:5">
       <c r="A3" s="4">
-        <v>2.2999999999999998</v>
+        <v>2.3</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>3</v>
@@ -1521,7 +2347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="27.5" customHeight="1">
+    <row r="4" ht="27.5" customHeight="1" spans="1:5">
       <c r="A4" s="4">
         <v>2.4</v>
       </c>
@@ -1533,7 +2359,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="27.5" customHeight="1">
+    <row r="5" ht="27.5" customHeight="1" spans="1:5">
       <c r="A5" s="4">
         <v>2.5</v>
       </c>
@@ -1546,7 +2372,7 @@
       </c>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" spans="1:5" ht="27.5" customHeight="1">
+    <row r="6" ht="27.5" customHeight="1" spans="1:5">
       <c r="A6" s="4">
         <v>2.6</v>
       </c>
@@ -1561,7 +2387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="27.5" customHeight="1">
+    <row r="7" ht="27.5" customHeight="1" spans="1:5">
       <c r="A7" s="4">
         <v>2.7</v>
       </c>
@@ -1576,7 +2402,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="27.5" customHeight="1">
+    <row r="8" ht="27.5" customHeight="1" spans="1:5">
       <c r="A8" s="1">
         <v>2.8</v>
       </c>
@@ -1591,94 +2417,103 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="27.5" customHeight="1">
+    <row r="9" ht="27.5" customHeight="1" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="27.5" customHeight="1">
+    <row r="10" ht="27.5" customHeight="1" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="41.5" customHeight="1">
+    <row r="11" ht="41.5" customHeight="1" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="41.5" customHeight="1">
+    <row r="12" ht="41.5" customHeight="1" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="41.5" customHeight="1">
+    <row r="13" ht="41.5" customHeight="1" spans="1:5">
       <c r="A13" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" ht="41.5" customHeight="1" spans="1:5">
+      <c r="A14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" ht="27.5" customHeight="1" spans="1:5">
+      <c r="A15" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="27.5" customHeight="1">
-      <c r="A14" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
+    <row r="16" ht="27.5" customHeight="1" spans="1:5">
+      <c r="A16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="15" spans="1:5" ht="27.5" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="27.5" customHeight="1"/>
     <row r="17" ht="27.5" customHeight="1"/>
     <row r="18" ht="27.5" customHeight="1"/>
     <row r="19" ht="27.5" customHeight="1"/>
@@ -1686,19 +2521,21 @@
     <row r="21" ht="27.5" customHeight="1"/>
     <row r="22" ht="27.5" customHeight="1"/>
     <row r="23" ht="27.5" customHeight="1"/>
-    <row r="24" ht="24" customHeight="1"/>
+    <row r="24" ht="27.5" customHeight="1"/>
     <row r="25" ht="24" customHeight="1"/>
     <row r="26" ht="24" customHeight="1"/>
     <row r="27" ht="24" customHeight="1"/>
     <row r="28" ht="24" customHeight="1"/>
     <row r="29" ht="24" customHeight="1"/>
     <row r="30" ht="24" customHeight="1"/>
+    <row r="31" ht="24" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/TITAN_A5/BD.xlsx
+++ b/TITAN_A5/BD.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1092,6 +1092,15 @@
     <t>2.14</t>
   </si>
   <si>
+    <t>parameters_A5-3_0001.bin</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>Сетка с 4.000.000 ячеек. Достаточно подробная. 10.000 шагов делает за 7 минут. Время за шаг около 1.3 10^-4</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">dd </t>
     </r>
@@ -1156,7 +1165,7 @@
         <rFont val="Consolas"/>
         <charset val="204"/>
       </rPr>
-      <t>0.7</t>
+      <t>0.5</t>
     </r>
     <r>
       <rPr>
@@ -1284,28 +1293,13 @@
       </rPr>
       <t>))</t>
     </r>
-  </si>
-  <si>
-    <t>parameters_A5-3_0001.bin</t>
-  </si>
-  <si>
-    <t>3.1</t>
-  </si>
-  <si>
-    <t>Сетка с 4.000.000 ячеек. Достаточно подробная. 10.000 шагов делает за 7 минут. Время за шаг около 1.3 10^-4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="28">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1350,150 +1344,6 @@
       <charset val="204"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Consolas"/>
@@ -1512,201 +1362,15 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1714,253 +1378,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1986,58 +1408,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
-    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
-    <cellStyle name="Процент" xfId="3" builtinId="5"/>
-    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
-    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
-    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
-    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
-    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
-    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
-    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
-    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
-    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
-    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
-    <cellStyle name="Итого" xfId="21" builtinId="25"/>
-    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
-    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
-    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
-    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
-    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
-    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
-    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
-    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
-    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2299,31 +1680,33 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="18.8148148148148" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7222222222222" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22.0925925925926" style="2" customWidth="1"/>
-    <col min="4" max="4" width="79.6296296296296" style="2" customWidth="1"/>
-    <col min="5" max="5" width="109.361111111111" style="3" customWidth="1"/>
-    <col min="6" max="12" width="8.72222222222222" style="3"/>
+    <col min="1" max="1" width="18.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.08984375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="79.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="109.36328125" style="3" customWidth="1"/>
+    <col min="6" max="12" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="29" customHeight="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="29" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
     </row>
-    <row r="2" ht="27.5" customHeight="1" spans="1:5">
+    <row r="2" spans="1:5" ht="27.5" customHeight="1">
       <c r="A2" s="4">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -2333,9 +1716,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="27.5" customHeight="1" spans="1:5">
+    <row r="3" spans="1:5" ht="27.5" customHeight="1">
       <c r="A3" s="4">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>3</v>
@@ -2347,7 +1730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="27.5" customHeight="1" spans="1:5">
+    <row r="4" spans="1:5" ht="27.5" customHeight="1">
       <c r="A4" s="4">
         <v>2.4</v>
       </c>
@@ -2359,7 +1742,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="27.5" customHeight="1" spans="1:5">
+    <row r="5" spans="1:5" ht="27.5" customHeight="1">
       <c r="A5" s="4">
         <v>2.5</v>
       </c>
@@ -2372,7 +1755,7 @@
       </c>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" ht="27.5" customHeight="1" spans="1:5">
+    <row r="6" spans="1:5" ht="27.5" customHeight="1">
       <c r="A6" s="4">
         <v>2.6</v>
       </c>
@@ -2387,7 +1770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="27.5" customHeight="1" spans="1:5">
+    <row r="7" spans="1:5" ht="27.5" customHeight="1">
       <c r="A7" s="4">
         <v>2.7</v>
       </c>
@@ -2402,7 +1785,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" ht="27.5" customHeight="1" spans="1:5">
+    <row r="8" spans="1:5" ht="27.5" customHeight="1">
       <c r="A8" s="1">
         <v>2.8</v>
       </c>
@@ -2417,7 +1800,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="27.5" customHeight="1" spans="1:5">
+    <row r="9" spans="1:5" ht="27.5" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -2431,7 +1814,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" ht="27.5" customHeight="1" spans="1:5">
+    <row r="10" spans="1:5" ht="27.5" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
@@ -2445,7 +1828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" ht="41.5" customHeight="1" spans="1:5">
+    <row r="11" spans="1:5" ht="41.5" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
@@ -2459,7 +1842,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" ht="41.5" customHeight="1" spans="1:5">
+    <row r="12" spans="1:5" ht="41.5" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
@@ -2471,7 +1854,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" ht="41.5" customHeight="1" spans="1:5">
+    <row r="13" spans="1:5" ht="41.5" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>23</v>
       </c>
@@ -2483,7 +1866,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" ht="41.5" customHeight="1" spans="1:5">
+    <row r="14" spans="1:5" ht="41.5" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>25</v>
       </c>
@@ -2492,17 +1875,19 @@
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="27.5" customHeight="1">
+      <c r="A15" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
     </row>
-    <row r="15" ht="27.5" customHeight="1" spans="1:5">
-      <c r="A15" s="1" t="s">
+    <row r="16" spans="1:5" ht="27.5" customHeight="1">
+      <c r="A16" s="1" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="16" ht="27.5" customHeight="1" spans="1:5">
-      <c r="A16" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>13</v>
@@ -2511,7 +1896,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" ht="27.5" customHeight="1"/>
@@ -2536,6 +1921,5 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/TITAN_A5/BD.xlsx
+++ b/TITAN_A5/BD.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1092,6 +1092,206 @@
     <t>2.14</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">dd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> par_pi_8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> dev_time_all</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
     <t>parameters_A5-3_0001.bin</t>
   </si>
   <si>
@@ -1099,207 +1299,19 @@
   </si>
   <si>
     <t>Сетка с 4.000.000 ячеек. Достаточно подробная. 10.000 шагов делает за 7 минут. Время за шаг около 1.3 10^-4</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">dd </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>1.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>0.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>sin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>2.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> par_pi_8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> dev_time_all</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>0.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>))</t>
-    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1344,6 +1356,150 @@
       <charset val="204"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Consolas"/>
@@ -1362,15 +1518,201 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1378,11 +1720,253 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1408,17 +1992,58 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
+    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
+    <cellStyle name="Процент" xfId="3" builtinId="5"/>
+    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
+    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
+    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
+    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
+    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
+    <cellStyle name="Итого" xfId="21" builtinId="25"/>
+    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
+    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
+    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1680,33 +2305,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22.08984375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="79.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="109.36328125" style="3" customWidth="1"/>
-    <col min="6" max="12" width="8.7265625" style="3"/>
+    <col min="1" max="1" width="18.8148148148148" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7222222222222" style="2" customWidth="1"/>
+    <col min="3" max="3" width="28.4444444444444" style="2" customWidth="1"/>
+    <col min="4" max="4" width="79.6296296296296" style="2" customWidth="1"/>
+    <col min="5" max="5" width="109.361111111111" style="3" customWidth="1"/>
+    <col min="6" max="12" width="8.72222222222222" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="29" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" ht="29" customHeight="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
     </row>
-    <row r="2" spans="1:5" ht="27.5" customHeight="1">
+    <row r="2" ht="27.5" customHeight="1" spans="1:5">
       <c r="A2" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -1716,9 +2339,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="27.5" customHeight="1">
+    <row r="3" ht="27.5" customHeight="1" spans="1:5">
       <c r="A3" s="4">
-        <v>2.2999999999999998</v>
+        <v>2.3</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>3</v>
@@ -1730,7 +2353,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="27.5" customHeight="1">
+    <row r="4" ht="27.5" customHeight="1" spans="1:5">
       <c r="A4" s="4">
         <v>2.4</v>
       </c>
@@ -1742,7 +2365,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="27.5" customHeight="1">
+    <row r="5" ht="27.5" customHeight="1" spans="1:5">
       <c r="A5" s="4">
         <v>2.5</v>
       </c>
@@ -1755,7 +2378,7 @@
       </c>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" spans="1:5" ht="27.5" customHeight="1">
+    <row r="6" ht="27.5" customHeight="1" spans="1:5">
       <c r="A6" s="4">
         <v>2.6</v>
       </c>
@@ -1770,7 +2393,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="27.5" customHeight="1">
+    <row r="7" ht="27.5" customHeight="1" spans="1:5">
       <c r="A7" s="4">
         <v>2.7</v>
       </c>
@@ -1785,7 +2408,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="27.5" customHeight="1">
+    <row r="8" ht="27.5" customHeight="1" spans="1:5">
       <c r="A8" s="1">
         <v>2.8</v>
       </c>
@@ -1800,7 +2423,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="27.5" customHeight="1">
+    <row r="9" ht="27.5" customHeight="1" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -1814,7 +2437,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="27.5" customHeight="1">
+    <row r="10" ht="27.5" customHeight="1" spans="1:5">
       <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
@@ -1828,7 +2451,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="41.5" customHeight="1">
+    <row r="11" ht="51" customHeight="1" spans="1:5">
       <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
@@ -1842,7 +2465,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="41.5" customHeight="1">
+    <row r="12" ht="41.5" customHeight="1" spans="1:5">
       <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
@@ -1854,7 +2477,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="41.5" customHeight="1">
+    <row r="13" ht="41.5" customHeight="1" spans="1:5">
       <c r="A13" s="4" t="s">
         <v>23</v>
       </c>
@@ -1866,7 +2489,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="41.5" customHeight="1">
+    <row r="14" ht="41.5" customHeight="1" spans="1:5">
       <c r="A14" s="4" t="s">
         <v>25</v>
       </c>
@@ -1875,19 +2498,17 @@
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="27.5" customHeight="1">
-      <c r="A15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
+    <row r="15" ht="27.5" customHeight="1" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="16" spans="1:5" ht="27.5" customHeight="1">
+    <row r="16" ht="27.5" customHeight="1" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>13</v>
@@ -1896,7 +2517,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="27.5" customHeight="1"/>
@@ -1921,5 +2542,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/TITAN_A5/BD.xlsx
+++ b/TITAN_A5/BD.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="30720" windowHeight="13440"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -890,12 +890,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
       <t xml:space="preserve">dd </t>
     </r>
     <r>

--- a/TITAN_A5/BD.xlsx
+++ b/TITAN_A5/BD.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13440"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="11020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1298,14 +1298,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="28">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1350,150 +1344,6 @@
       <charset val="204"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Consolas"/>
@@ -1512,7 +1362,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1521,192 +1371,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1716,251 +1386,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1986,58 +1429,26 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
-    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
-    <cellStyle name="Процент" xfId="3" builtinId="5"/>
-    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
-    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
-    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
-    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
-    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
-    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
-    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
-    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
-    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
-    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
-    <cellStyle name="Итого" xfId="21" builtinId="25"/>
-    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
-    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
-    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
-    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
-    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
-    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
-    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
-    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
-    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2299,31 +1710,33 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="18.8148148148148" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7222222222222" style="2" customWidth="1"/>
-    <col min="3" max="3" width="28.4444444444444" style="2" customWidth="1"/>
-    <col min="4" max="4" width="79.6296296296296" style="2" customWidth="1"/>
-    <col min="5" max="5" width="109.361111111111" style="3" customWidth="1"/>
-    <col min="6" max="12" width="8.72222222222222" style="3"/>
+    <col min="1" max="1" width="18.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="79.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="109.36328125" style="3" customWidth="1"/>
+    <col min="6" max="12" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="29" customHeight="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="29" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
     </row>
-    <row r="2" ht="27.5" customHeight="1" spans="1:5">
+    <row r="2" spans="1:5" ht="27.5" customHeight="1">
       <c r="A2" s="4">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -2333,9 +1746,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="27.5" customHeight="1" spans="1:5">
+    <row r="3" spans="1:5" ht="27.5" customHeight="1">
       <c r="A3" s="4">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>3</v>
@@ -2347,7 +1760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="27.5" customHeight="1" spans="1:5">
+    <row r="4" spans="1:5" ht="27.5" customHeight="1">
       <c r="A4" s="4">
         <v>2.4</v>
       </c>
@@ -2359,7 +1772,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="27.5" customHeight="1" spans="1:5">
+    <row r="5" spans="1:5" ht="27.5" customHeight="1">
       <c r="A5" s="4">
         <v>2.5</v>
       </c>
@@ -2372,8 +1785,8 @@
       </c>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" ht="27.5" customHeight="1" spans="1:5">
-      <c r="A6" s="4">
+    <row r="6" spans="1:5" ht="27.5" customHeight="1">
+      <c r="A6" s="11">
         <v>2.6</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -2387,7 +1800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="27.5" customHeight="1" spans="1:5">
+    <row r="7" spans="1:5" ht="27.5" customHeight="1">
       <c r="A7" s="4">
         <v>2.7</v>
       </c>
@@ -2402,8 +1815,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" ht="27.5" customHeight="1" spans="1:5">
-      <c r="A8" s="1">
+    <row r="8" spans="1:5" ht="27.5" customHeight="1">
+      <c r="A8" s="13">
         <v>2.8</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -2417,8 +1830,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="27.5" customHeight="1" spans="1:5">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:5" ht="27.5" customHeight="1">
+      <c r="A9" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -2431,7 +1844,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" ht="27.5" customHeight="1" spans="1:5">
+    <row r="10" spans="1:5" ht="27.5" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
@@ -2445,8 +1858,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" ht="51" customHeight="1" spans="1:5">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:5" ht="51" customHeight="1">
+      <c r="A11" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -2459,8 +1872,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" ht="41.5" customHeight="1" spans="1:5">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:5" ht="41.5" customHeight="1">
+      <c r="A12" s="12" t="s">
         <v>21</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -2471,8 +1884,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" ht="41.5" customHeight="1" spans="1:5">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:5" ht="41.5" customHeight="1">
+      <c r="A13" s="12" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -2483,8 +1896,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" ht="41.5" customHeight="1" spans="1:5">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:5" ht="41.5" customHeight="1">
+      <c r="A14" s="12" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -2495,12 +1908,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" ht="27.5" customHeight="1" spans="1:5">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:5" ht="27.5" customHeight="1">
+      <c r="A15" s="9" t="s">
         <v>27</v>
       </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
     </row>
-    <row r="16" ht="27.5" customHeight="1" spans="1:5">
+    <row r="16" spans="1:5" ht="27.5" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
@@ -2536,6 +1951,5 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/TITAN_A5/BD.xlsx
+++ b/TITAN_A5/BD.xlsx
@@ -1362,7 +1362,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1372,6 +1372,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1403,7 +1409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1429,12 +1435,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1442,6 +1442,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1728,11 +1740,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="29" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
     </row>
     <row r="2" spans="1:5" ht="27.5" customHeight="1">
       <c r="A2" s="4">
@@ -1786,7 +1798,7 @@
       <c r="E5" s="8"/>
     </row>
     <row r="6" spans="1:5" ht="27.5" customHeight="1">
-      <c r="A6" s="11">
+      <c r="A6" s="9">
         <v>2.6</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -1816,7 +1828,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="27.5" customHeight="1">
-      <c r="A8" s="13">
+      <c r="A8" s="15">
         <v>2.8</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -1831,7 +1843,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="27.5" customHeight="1">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="11" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -1859,7 +1871,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="51" customHeight="1">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -1873,7 +1885,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="41.5" customHeight="1">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -1885,7 +1897,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="41.5" customHeight="1">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -1897,7 +1909,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="41.5" customHeight="1">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="10" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -1909,11 +1921,11 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="27.5" customHeight="1">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
     </row>
     <row r="16" spans="1:5" ht="27.5" customHeight="1">
       <c r="A16" s="1" t="s">

--- a/TITAN_A5/BD.xlsx
+++ b/TITAN_A5/BD.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
   <si>
     <t>parameters_A5-2_0001.bin</t>
   </si>
@@ -677,22 +677,16 @@
     <t>2.4 пересчитал новой схемой</t>
   </si>
   <si>
-    <t>2.11</t>
-  </si>
-  <si>
     <t>2.4 пересчитал новой схемой (меньше ограничений)</t>
   </si>
   <si>
     <t>2.12</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
+    <t>2.13</t>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">dd </t>
     </r>
     <r>
@@ -756,6 +750,415 @@
         <rFont val="Consolas"/>
         <charset val="204"/>
       </rPr>
+      <t>0.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> par_pi_8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> dev_time_all</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
+    <t>2.14</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">dd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> par_pi_8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> dev_time_all</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
+    <t>parameters_A5-3_0001.bin</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>Сетка с 4.000.000 ячеек. Достаточно подробная. 10.000 шагов делает за 7 минут. Время за шаг около 1.3 10^-4</t>
+  </si>
+  <si>
+    <t>2.11-7</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
       <t>0.1</t>
     </r>
     <r>
@@ -882,417 +1285,202 @@
         <rFont val="Consolas"/>
         <charset val="204"/>
       </rPr>
+      <t>))  0.217237</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> par_pi_8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> dev_time_all</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>3.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
       <t>))</t>
     </r>
-  </si>
-  <si>
-    <t>2.13</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">dd </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>1.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>0.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>sin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>2.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> par_pi_8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> dev_time_all</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>0.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>))</t>
-    </r>
-  </si>
-  <si>
-    <t>2.14</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve">dd </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>1.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>0.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>sin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>2.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> par_pi_8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> dev_time_all</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>0.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>))</t>
-    </r>
-  </si>
-  <si>
-    <t>parameters_A5-3_0001.bin</t>
-  </si>
-  <si>
-    <t>3.1</t>
-  </si>
-  <si>
-    <t>Сетка с 4.000.000 ячеек. Достаточно подробная. 10.000 шагов делает за 7 минут. Время за шаг около 1.3 10^-4</t>
   </si>
 </sst>
 </file>
@@ -1444,16 +1632,16 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1740,11 +1928,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="29" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="27.5" customHeight="1">
       <c r="A2" s="4">
@@ -1806,7 +1994,7 @@
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="7" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>10</v>
@@ -1828,7 +2016,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="27.5" customHeight="1">
-      <c r="A8" s="15">
+      <c r="A8" s="13">
         <v>2.8</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -1871,14 +2059,14 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="51" customHeight="1">
-      <c r="A11" s="14" t="s">
-        <v>19</v>
+      <c r="A11" s="12" t="s">
+        <v>28</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>6</v>
@@ -1886,50 +2074,50 @@
     </row>
     <row r="12" spans="1:5" ht="41.5" customHeight="1">
       <c r="A12" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="7" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="41.5" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="41.5" customHeight="1">
       <c r="A14" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="27.5" customHeight="1">
-      <c r="A15" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
+      <c r="A15" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
     </row>
     <row r="16" spans="1:5" ht="27.5" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>13</v>
@@ -1938,7 +2126,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" ht="27.5" customHeight="1"/>

--- a/TITAN_A5/BD.xlsx
+++ b/TITAN_A5/BD.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="11020"/>
+    <workbookView windowWidth="28800" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>parameters_A5-2_0001.bin</t>
   </si>
@@ -677,16 +677,225 @@
     <t>2.4 пересчитал новой схемой</t>
   </si>
   <si>
+    <t>2.11-7</t>
+  </si>
+  <si>
     <t>2.4 пересчитал новой схемой (меньше ограничений)</t>
   </si>
   <si>
     <t>2.12</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">dd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> par_pi_8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> dev_time_all</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD4922F"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
+      <t>))  0.217237</t>
+    </r>
+  </si>
+  <si>
     <t>2.13</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <charset val="204"/>
+      </rPr>
       <t xml:space="preserve">dd </t>
     </r>
     <r>
@@ -1090,404 +1299,19 @@
   </si>
   <si>
     <t>Сетка с 4.000.000 ячеек. Достаточно подробная. 10.000 шагов делает за 7 минут. Время за шаг около 1.3 10^-4</t>
-  </si>
-  <si>
-    <t>2.11-7</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">dd </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>1.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>0.1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>sin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>2.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> par_pi_8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> dev_time_all</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>0.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>))  0.217237</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">dd </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>1.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>0.7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>sin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>2.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> par_pi_8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> dev_time_all</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD4922F"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>3.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3B3B3B"/>
-        <rFont val="Consolas"/>
-        <charset val="204"/>
-      </rPr>
-      <t>))</t>
-    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1532,6 +1356,150 @@
       <charset val="204"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Consolas"/>
@@ -1550,7 +1518,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1559,7 +1527,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1569,8 +1537,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1580,24 +1734,266 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1626,29 +2022,70 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
+    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
+    <cellStyle name="Процент" xfId="3" builtinId="5"/>
+    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
+    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
+    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
+    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
+    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
+    <cellStyle name="Итого" xfId="21" builtinId="25"/>
+    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
+    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
+    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1910,33 +2347,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="28.453125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="79.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="109.36328125" style="3" customWidth="1"/>
-    <col min="6" max="12" width="8.7265625" style="3"/>
+    <col min="1" max="1" width="18.8148148148148" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7222222222222" style="2" customWidth="1"/>
+    <col min="3" max="3" width="28.4537037037037" style="2" customWidth="1"/>
+    <col min="4" max="4" width="79.6296296296296" style="2" customWidth="1"/>
+    <col min="5" max="5" width="109.361111111111" style="3" customWidth="1"/>
+    <col min="6" max="12" width="8.72222222222222" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="29" customHeight="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" ht="29" customHeight="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="27.5" customHeight="1">
+    <row r="2" ht="27.5" customHeight="1" spans="1:5">
       <c r="A2" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -1946,9 +2381,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="27.5" customHeight="1">
+    <row r="3" ht="27.5" customHeight="1" spans="1:5">
       <c r="A3" s="4">
-        <v>2.2999999999999998</v>
+        <v>2.3</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>3</v>
@@ -1960,7 +2395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="27.5" customHeight="1">
+    <row r="4" ht="27.5" customHeight="1" spans="1:5">
       <c r="A4" s="4">
         <v>2.4</v>
       </c>
@@ -1972,7 +2407,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="27.5" customHeight="1">
+    <row r="5" ht="27.5" customHeight="1" spans="1:5">
       <c r="A5" s="4">
         <v>2.5</v>
       </c>
@@ -1985,7 +2420,7 @@
       </c>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" spans="1:5" ht="27.5" customHeight="1">
+    <row r="6" ht="27.5" customHeight="1" spans="1:5">
       <c r="A6" s="9">
         <v>2.6</v>
       </c>
@@ -1994,13 +2429,13 @@
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="7" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="27.5" customHeight="1">
+    <row r="7" ht="27.5" customHeight="1" spans="1:5">
       <c r="A7" s="4">
         <v>2.7</v>
       </c>
@@ -2015,8 +2450,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="27.5" customHeight="1">
-      <c r="A8" s="13">
+    <row r="8" ht="27.5" customHeight="1" spans="1:5">
+      <c r="A8" s="10">
         <v>2.8</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -2030,7 +2465,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="27.5" customHeight="1">
+    <row r="9" ht="39" customHeight="1" spans="1:5">
       <c r="A9" s="11" t="s">
         <v>15</v>
       </c>
@@ -2044,7 +2479,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="27.5" customHeight="1">
+    <row r="10" ht="37" customHeight="1" spans="1:5">
       <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
@@ -2058,66 +2493,64 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="51" customHeight="1">
+    <row r="11" ht="51" customHeight="1" spans="1:5">
       <c r="A11" s="12" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="41.5" customHeight="1">
-      <c r="A12" s="10" t="s">
-        <v>20</v>
+    <row r="12" ht="41.5" customHeight="1" spans="1:5">
+      <c r="A12" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="7" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="41.5" customHeight="1">
-      <c r="A13" s="10" t="s">
-        <v>21</v>
+    <row r="13" ht="41.5" customHeight="1" spans="1:5">
+      <c r="A13" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="41.5" customHeight="1">
-      <c r="A14" s="10" t="s">
-        <v>23</v>
+    <row r="14" ht="41.5" customHeight="1" spans="1:5">
+      <c r="A14" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="27.5" customHeight="1">
-      <c r="A15" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
+    <row r="15" ht="27.5" customHeight="1" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="16" spans="1:5" ht="27.5" customHeight="1">
+    <row r="16" ht="27.5" customHeight="1" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>13</v>
@@ -2126,7 +2559,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="27.5" customHeight="1"/>
@@ -2151,5 +2584,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/TITAN_A5/BD.xlsx
+++ b/TITAN_A5/BD.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12360"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
   <si>
     <t>parameters_A5-2_0001.bin</t>
   </si>
@@ -251,6 +251,9 @@
       </rPr>
       <t>))</t>
     </r>
+  </si>
+  <si>
+    <t>2,6-2</t>
   </si>
   <si>
     <t>HLL + HLLD</t>
@@ -1518,7 +1521,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1708,12 +1711,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1986,10 +1983,10 @@
     <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2421,18 +2418,18 @@
       <c r="E5" s="8"/>
     </row>
     <row r="6" ht="27.5" customHeight="1" spans="1:5">
-      <c r="A6" s="9">
-        <v>2.6</v>
+      <c r="A6" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" ht="27.5" customHeight="1" spans="1:5">
@@ -2444,10 +2441,10 @@
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" ht="27.5" customHeight="1" spans="1:5">
@@ -2455,39 +2452,39 @@
         <v>2.8</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" ht="39" customHeight="1" spans="1:5">
       <c r="A9" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" ht="37" customHeight="1" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>6</v>
@@ -2495,13 +2492,13 @@
     </row>
     <row r="11" ht="51" customHeight="1" spans="1:5">
       <c r="A11" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>6</v>
@@ -2509,57 +2506,57 @@
     </row>
     <row r="12" ht="41.5" customHeight="1" spans="1:5">
       <c r="A12" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" ht="41.5" customHeight="1" spans="1:5">
       <c r="A13" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" ht="41.5" customHeight="1" spans="1:5">
       <c r="A14" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" ht="27.5" customHeight="1" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" ht="27.5" customHeight="1" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="27.5" customHeight="1"/>

--- a/TITAN_A5/BD.xlsx
+++ b/TITAN_A5/BD.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="23232" windowHeight="9972"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="32">
   <si>
     <t>parameters_A5-2_0001.bin</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>там где-то плотность отрицательной становится - надо исправлять</t>
+  </si>
+  <si>
+    <t>2,7-2</t>
   </si>
   <si>
     <r>
@@ -2433,18 +2436,18 @@
       </c>
     </row>
     <row r="7" ht="27.5" customHeight="1" spans="1:5">
-      <c r="A7" s="4">
-        <v>2.7</v>
+      <c r="A7" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" ht="27.5" customHeight="1" spans="1:5">
@@ -2452,39 +2455,39 @@
         <v>2.8</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" ht="39" customHeight="1" spans="1:5">
       <c r="A9" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" ht="37" customHeight="1" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>6</v>
@@ -2492,13 +2495,13 @@
     </row>
     <row r="11" ht="51" customHeight="1" spans="1:5">
       <c r="A11" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>6</v>
@@ -2506,57 +2509,57 @@
     </row>
     <row r="12" ht="41.5" customHeight="1" spans="1:5">
       <c r="A12" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="41.5" customHeight="1" spans="1:5">
       <c r="A13" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" ht="41.5" customHeight="1" spans="1:5">
       <c r="A14" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="27.5" customHeight="1" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" ht="27.5" customHeight="1" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" ht="27.5" customHeight="1"/>
